--- a/docs/QA-Dev-Work-Log.xlsx
+++ b/docs/QA-Dev-Work-Log.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sonar Findings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bugs Fixed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Smoke Test Results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Known Issues (Not Fixed)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Manual Commands &amp; Server" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sonar Findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bugs Fixed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Smoke Test Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Known Issues (Not Fixed)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +60,20 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Courier New"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -76,7 +91,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9F2D9"/>
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,7 +106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D9F2D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,28 +149,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -584,7 +614,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Manual Commands &amp; Server</t>
         </is>
       </c>
     </row>
@@ -701,162 +731,208 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>7. QA: smoke testing</t>
+          <t>6b. Database schema change</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Hit all 34 application routes with an authenticated session</t>
+          <t>Added invoice.ewaybilldate column directly via ALTER TABLE — required for invoice creation to work at all</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>27 pass, 7 fail (all pre-existing, documented, none caused by this work)</t>
+          <t>Applied to local dev DB only — MUST be applied manually to any other environment</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Smoke Test Results</t>
+          <t>Manual Commands &amp; Server</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>8. QA: functional testing</t>
+          <t>7. QA: smoke testing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>End-to-end tested invoice creation, payment recording, inventory update, product creation against real form submissions</t>
+          <t>Hit all 34 application routes with an authenticated session</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>All 5 core flows verified passing after fixes</t>
+          <t>27 pass, 7 fail (all pre-existing, documented, none caused by this work)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Bugs Fixed</t>
+          <t>Smoke Test Results</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>9. Known issues (not fixed)</t>
+          <t>8. QA: functional testing</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Documented real, confirmed bugs found along the way that were out of scope for this pass</t>
+          <t>End-to-end tested invoice creation, payment recording, inventory update, product creation against real form submissions</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>5 issues logged for a future scoping decision</t>
+          <t>All 5 core flows verified passing after fixes</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Known Issues (Not Fixed)</t>
+          <t>Bugs Fixed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>9. Known issues (not fixed)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Documented real, confirmed bugs found along the way that were out of scope for this pass</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>5 issues logged for a future scoping decision</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Known Issues (Not Fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>10. Git</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Committed and pushed all fixes across two commits to origin/meet-update</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Committed and pushed all fixes across three commits to origin/meet-update</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pushed — see commit log below</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Commit log (this repo, branch meet-update)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Message</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>4c39c24</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Initial project import for meet-update</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>41d6dab</t>
+          <t>4c39c24</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fix Sonar Blocker and Critical issues (backend + frontend)</t>
+          <t>Initial project import for meet-update</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>41d6dab</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Fix Sonar Blocker and Critical issues (backend + frontend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>b4e5550</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Fix Sonar High/Medium issues and critical invoice/payment bugs</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>⚠ Manual step required outside git</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>e729fa1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Add QA/dev work log spreadsheet documenting the full fix pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>(this commit)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Add manual commands / server &amp; database change runbook to the work log</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>⚠ Manual step required outside git — see 'Manual Commands &amp; Server' sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A database column (invoice.ewaybilldate) was added directly via ALTER TABLE on the local dev DB, because this database predates Laravel's migration system (imported from a raw SQL dump, no migrations table). This is NOT captured by any git commit — it must be applied by hand to any other environment (staging/production/teammate's machine):</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ALTER TABLE invoice ADD COLUMN ewaybilldate DATE NULL AFTER ewaybillno;</t>
         </is>
@@ -872,6 +948,500 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Manual Commands &amp; Server / Database Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Everything outside git — run these when setting up a new environment or deploying. NOT auto-applied by pulling the branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>🔴 MUST RUN on every environment (staging / production / a teammate's machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Command / Change</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>ALTER TABLE invoice ADD COLUMN ewaybilldate DATE NULL AFTER ewaybillno;</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>MySQL, on the application database</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Column the app code has always expected but was never created. Without it, invoice creation fails (HTTP 500) on every submission — see Bugs Fixed sheet, bug #1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>🟡 Fresh environment / new server setup (from zero)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>1. Install PHP 8.2</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>brew install php@8.2   (or apt/yum equivalent on Linux servers)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Server / host machine</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>composer.json requires "php": "^8.1"; app was built and tested against 8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2. Install MySQL</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>brew install mysql   (most hosts already provide this)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Server / host machine</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Application database engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>3. Install Composer</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>brew install composer</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Server / host machine</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>PHP dependency manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>4. Install PHP dependencies</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>composer install</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Project root</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Installs vendor/ — Laravel framework + packages</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>5. Install JS dependencies</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>npm install</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Project root</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Only needed if rebuilding frontend assets; the compiled build/ folder is already committed to the repo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>6. Create the database + user</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>CREATE DATABASE u411614341_Invoice; CREATE USER 'u411614341_invoice'@'...' IDENTIFIED BY '...'; GRANT ALL PRIVILEGES ON u411614341_Invoice.* TO ...;</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Matches the credentials already configured in .env — see .env.example for the expected variable names</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>7. Import the database schema + data</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>mysql -u root u411614341_Invoice &lt; "u411614341_Invoice (2).sql"</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>MySQL, from the project root</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Base schema and any seed data. This SQL dump does not include the invoice/customer/product tables' full production data — see Notes below</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>8. Apply the ewaybilldate fix</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>See the MUST RUN row above</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Required — the SQL dump does not include this column</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>9. Configure environment</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Copy .env.example to .env, set DB_* credentials, APP_URL, APP_KEY</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Project root</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>php artisan key:generate if APP_KEY is blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>10. Set the web server document root</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Point the web server's document root at the PROJECT ROOT itself, not a public/ subfolder</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Web server config (Apache/Nginx/hosting panel)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>This app is a shared-hosting style deployment — index.php, vendor/, bootstrap/ all sit at the repo root (see Notes below). This is NOT the standard Laravel public/ layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>⚪ Local development convenience only — do NOT need these on a real server</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Command / File</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Why it's dev-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>public/build symlink</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>ln -s ../build public/build</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Lets the built-in PHP dev server find compiled CSS/JS at the URL path Blade templates expect</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Only needed for `php artisan serve` / `php -S` style local testing. A real Apache/Nginx host serving the whole repo as document root already resolves build/ at the correct path without this symlink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>router.php</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Custom router script for PHP's built-in server, not part of the Laravel app</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Makes `php -S 127.0.0.1:8000 router.php` correctly serve static files from the repo root instead of expecting a public/ folder</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Apache/Nginx don't need a router script — they're configured via vhost/.htaccess instead. Untracked in git.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>sonar-project.properties</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>SonarQube scanner config</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Lets a teammate re-run the same static-analysis scan locally</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Not part of the running application; safe to keep or delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Local SonarQube (Docker)</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>docker run -d --name sonarqube -p 9000:9000 sonarqube:community</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Ran a local code-quality dashboard for the Sonar cleanup pass</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>One-off analysis tooling, not part of the deployed app. See the Sonar Findings sheet for results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>• Document root: this repo is deployed shared-hosting style — index.php, vendor/, bootstrap/, .env all sit directly at the project root (not inside a public/ folder as a standard Laravel app would). Confirm the hosting panel / vhost config points at the repo root, not a public/ subfolder that doesn't functionally exist here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>• The imported SQL dump (u411614341_Invoice (2).sql) is a partial export — some tables (invoice, customer) had little or no data at the time of import, which is why several bugs in the Bugs Fixed sheet only surfaced during live functional testing rather than on page load.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>• No other schema changes were made this pass beyond the ewaybilldate column. All other fixes were application code only (see Bugs Fixed and Sonar Findings sheets).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>• No new database tables were created and no existing tables were dropped or renamed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -935,130 +1505,130 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Blocker (Must-Fix)</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Dead IE8/9 CSS hack in vendor flatpickr theme file — removed, zero visual change</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="18" t="n">
         <v>59</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="18" t="n">
         <v>57</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>2 remaining are stock Laravel config scaffolding (127.0.0.1 / log path duplication) — won't-fix by design, matches every fresh Laravel install</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>High (Major)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="12" t="n">
         <v>497</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Partially fixed</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Remaining 431 dominated by false positives: 361 icon-font CSS declarations, 44 vendor-plugin duplicate CSS selectors (too risky to merge without visual regression testing), 11 correct Bootstrap ARIA patterns Sonar misflags</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Medium (Minor)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="18" t="n">
         <v>368</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="18" t="n">
         <v>353</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>Essentially cleared — mostly trailing whitespace and 101 real Subresource-Integrity hashes added to CDN scripts</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Info (Low)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>None were ever open</t>
         </is>
@@ -1094,282 +1664,282 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Removed dead/commented-out code (backend + frontend)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Zero behavior change; code was already inert</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>CORS wildcard origin</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Restricted to APP_URL; confirmed only affects an unused default /api/* stub route</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>50 duplicate HTML id attributes across 8 Blade views</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Renamed to unique ids; cross-checked against all JS to confirm nothing was silently broken</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>101 CDN scripts/styles missing Subresource Integrity (SRI)</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="18" t="n">
         <v>101</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Fetched exact bytes from each version-pinned CDN URL and computed real sha384 hashes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>3 CDN resources without SRI (SweetAlert2, TinyMCE, html2canvas)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>URLs are NOT version-pinned (e.g. .../tinymce/6/...) — a hardcoded hash would work today and silently break the app the next time that CDN updates its 'latest' build</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Invalid scope="row" attribute on &lt;td&gt; elements</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>HTML spec only allows scope on &lt;th&gt;; purely invalid markup, zero effect either way</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Trailing whitespace / missing final newlines</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>~260</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Purely mechanical, zero risk</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Form &lt;select&gt; elements not linked to a visible label</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>Linked via aria-labelledby to the real adjacent label cell instead of a copy-pasted Bootstrap-docs placeholder</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Logout link using href="javascript:void()" + onclick</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>Converted to a real &lt;button&gt;; tested logout end-to-end afterward</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>CSS font-family missing generic fallback</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="15" t="n">
         <v>361</v>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>All are icon-font glyph declarations (Line Awesome, Material Design Icons, remixicon) — a generic fallback is meaningless for icon glyphs</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Duplicate CSS selectors/properties in vendor plugin files</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Spread across 15+ third-party UI plugins (calendar, charts, editor...); merging risks silently changing cascade order with no way to visually regression-test each widget</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Prefer native &lt;progress&gt;/&lt;button&gt; over ARIA role</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>These are Bootstrap's own official patterns; swapping elements would require rebuilding CSS styling from scratch for a cosmetic lint preference</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Commented code inside vendor icon-font file</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>26,000-line auto-generated stylesheet, explicitly marked 'Not included in production' by the upstream library</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Empty CSS comments (rtlcss directives)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>These are /*rtl:begin:ignore*/ build directives controlling right-to-left layout for this app's Arabic locale — removing them breaks RTL support</t>
         </is>
@@ -1384,7 +1954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1448,180 +2018,180 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Invoice creation fails (HTTP 500) on every single submission</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>invoice.ewaybilldate column referenced by the app code has never existed in the database</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Added the missing nullable DATE column via ALTER TABLE (DB predates Laravel migrations, so a migration file wasn't the right mechanism here)</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Created a real invoice through the actual form end-to-end — succeeded</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Recording a payment against an invoice fails (HTTP 500)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>InvoiceController.php calls Paidamount::create() with no `use App\Models\Paidamount;` import — PHP resolved the bare class name to a non-existent class in the Controllers namespace</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Added the missing import statement</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Recorded a real payment via the actual endpoint — invoice paid/remaining amount updated correctly</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Requested</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Vendor page fails (HTTP 500)</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Query joined on invoice.customer_id, a column that doesn't exist — the real relationship is backwards (customer.invoice_id → invoice.id). Also never selected customer.name at all</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Fixed join direction and added the missing name column to the select list</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Page renders 200 and correctly displays real customer names and invoice numbers</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Requested</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Invoice Details page fails (HTTP 500)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Query selected product.product, a column that doesn't exist — the real column is product.name</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Aliased product.name AS product — required zero Blade template changes</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Page renders 200 and correctly displays the real product name on a real invoice</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Every product created through the UI silently saves with a blank name</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Product::$fillable listed 'product'; the actual form field (and the actual database column) is 'name'. Laravel's mass-assignment protection silently drops any field not in $fillable — no error, just missing data</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Corrected the fillable array to list 'name'</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Reproduced the bug live (submitted a real form, confirmed NULL saved), then confirmed the same submission saves correctly after the fix</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>CNC thickness values entered on the Technical Parameters page never save</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Same bug class as #5 — Cnsthinks::$fillable had a typo ('cnsthinks') that matched neither the real form field name nor the real column name (both are 'cuttingthinks')</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Corrected the fillable array</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Reproduced and confirmed fixed the same way as #5</t>
         </is>
@@ -1636,7 +2206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1688,482 +2258,482 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Dashboard / home</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr"/>
+      <c r="D4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>/product</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Product list</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
+      <c r="D5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>/apps-invoices-list</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Invoice list</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>/apps-invoices-create</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Invoice creation form</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>/invoiceddetails/{id}</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Invoice details view</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Fixed this session (bug #4)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>/paymenthistry</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Payment history list</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>/vender</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Vendor/customer list</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Fixed this session (bug #3)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>/inventrylist</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Inventory list</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>/standerconfig/{id}</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Product standard config page</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>/standerconfiglist/{id}</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Standard config list page</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>/TechnicalParameters/{id}</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Technical parameters page</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>/fiberqutation/{id}</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Fiber laser quotation form</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>/admin/listqutation</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Quotation list</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>/printquation/{id}</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Quotation PDF view</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="D17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>/admin/invoice/getproductvalue</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>AJAX: get product value</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>/admin/invoice/getproduct1 (with param)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>AJAX: get product value (variant)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>Initial 500 was a missing test parameter, not a bug</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>/register, /password/reset</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Auth utility pages</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
+      <c r="D20" s="18" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>/softerwere/{id}</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Add-software modal target view</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: returns view without required $id — see Known Issues sheet</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>/softerwere/show</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Software listing show-page</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: same missing-$id class of bug</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>/cutting/show</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Laser cutting show-page</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: controller method cuttingshow() was never implemented</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>/focusing/show</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Focusing show-page</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: controller method focusingshow() was never implemented</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>/power/show</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Power show-page</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: controller method powershow() was never implemented</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>/cuttingway/{id}</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Cutting way detail view</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: missing-$id class of bug</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>/co2quation</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>CO2 laser quotation form</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Pre-existing: shadowed by the app's catch-all route + controller requires an id the route never supplies</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
+      <c r="A28" s="22" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Total routes tested</t>
         </is>
@@ -2173,7 +2743,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Passing</t>
         </is>
@@ -2201,7 +2771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2259,135 +2829,135 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>~10 'Add Software / Laser Cutting / Focusing / Power / Motor / Gear / Rack' modal forms error after submit</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>High — real data-entry forms inside the product config pages appear broken to users</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Each *store() method in StanderconfigController / StanderconfiglistController / TechinalController returns view('standerconfig') without passing the $id the view requires — 'Undefined variable $id'</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Touches ~10 call sites across 3 controllers; the correct fix (likely passing $request-&gt;input('product_id')) should be confirmed per call site rather than batch-patched</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Fix each call site, passing the correct id; add a regression test per modal</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>3 dead routes: cutting/show, focusing/show, power/show</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Routes point to StanderconfigController@cuttingshow / focusingshow / powershow — none of these three methods were ever implemented (only softerwereshow exists)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Requires deciding what these pages should actually show — not a one-line fix</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Either implement the 3 missing methods or remove the dead routes, depending on product intent</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>co2quation route is unreachable</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Shadowed by the app's catch-all {any} route (registered earlier in routes/web.php), and the controller method requires an $id the route never supplies</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Found in an earlier session; fixing requires route re-ordering plus a route-signature decision</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Move the route above the catch-all and add the missing {id} parameter</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Laser Cutting Machine 'description' field never saves</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Three-way mismatch: the form sends 'details', the model's $fillable says 'description', the real database column is 'decription' (typo baked into the original table)</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Fixing the model alone won't fix this — the form field itself also needs to change; needs a decision on the intended canonical field name</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Decide the correct field name, then update form + model together</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Userdata model is fully dead code</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>None currently</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Points at a table ('user', singular) that doesn't match its own $fillable columns, and nothing in the app references this model anywhere</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Zero real-world impact since it's unused — not worth touching</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Safe to delete if confirmed unused, or leave as-is</t>
         </is>

--- a/docs/QA-Dev-Work-Log.xlsx
+++ b/docs/QA-Dev-Work-Log.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +76,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00B00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +113,11 @@
         <fgColor rgb="00D9F2D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -136,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +195,22 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -551,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -935,6 +960,415 @@
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ALTER TABLE invoice ADD COLUMN ewaybilldate DATE NULL AFTER ewaybillno;</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Session 2 (2026-07-16 to 2026-07-17): India localization, real data, backlog bug fixes, clean-architecture extension, first real test suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>What was done</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Detail sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>11. India localization</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Fixed timezone/currency/date formatting for India-only use; fixed GST logic bug (SGST+CGST vs IGST condition was inverted); removed all $ signs and non-Indian flags from UI</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>App fully India-localized; GST now calculates correctly for Gujarat vs other-state customers</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>12. Real business data + dashboard</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Cleared test data, seeded realistic Oracle Machine Tech data (laser cutting machines, real customers/invoices split Gujarat vs other-state); rewrote dashboard (HomeController::root()) from 100% Velzon demo content to real queries</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>Dashboard shows real revenue/invoices/customers/pending payments/top products/recent invoices instead of fake data</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>13. Git hygiene</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Added storage/framework/{cache,sessions,views}/* and storage/logs/*.log to .gitignore — these were showing as untracked noise on every session</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>git status is now meaningful; untracked cache files no longer prompt for commit</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>14. Backlog items 1-4: bug fixes</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Fixed 3 routes shadowed by the {any} catch-all (apps-invoices-list, vender, inventrylist), removed a dead invoice.status route, fixed invoice notes field being silently dropped on save, added missing placesupply validation</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>All 3 routes reachable and working; notes field now persists; empty placesupply shows a real error instead of a 500</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>15. Migrations backfill + test infrastructure (Phase 0)</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Wrote 18 new Laravel migrations for tables that only ever existed in the live DB with no migration history (invoice, customer, invoiceproduct, paidamount, bank, product + 10 product-config tables, invetry, quationform); wired up .env.testing + sqlite for real automated testing</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>php artisan migrate now works from zero on a fresh environment; test suite can actually run</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Manual Commands &amp; Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>16. Clean architecture: Inventory domain (Phase 1)</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Wrote tests/Feature/InventoryTest.php against original behavior, then refactored InventryController into Controller -&gt; Service -&gt; Repository, matching the existing Product Configuration pilot pattern</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>3 passing tests; behavior unchanged, verified against real live DB</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>17. Clean architecture: Quotation domain (Phase 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Wrote tests/Feature/QuotationTest.php, refactored QutationController the same way, extracted ~10 raw Eloquent queries that were embedded directly inside qutation.blade.php/co2qutation.blade.php into the new repository layer</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>5 passing tests; found 2 new pre-existing bugs (see Bugs Fixed) locked in by the tests, not fixed</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>18. Clean architecture: Home/Auth domain (Phase 3)</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Wrote tests/Feature/HomeTest.php, refactored HomeController (dashboard + profile/password) the same way; left the stock Laravel Auth/* scaffolding untouched (low value for this pattern)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>4 passing tests; testing this domain surfaced the guest-500 bug fixed in phase 20 below</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>19. Clean architecture: Invoice domain (Phase 4, largest)</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>Wrote tests/Feature/InvoiceTest.php (10 tests), refactored InvoiceController (315 lines, 10 methods, the biggest controller in the app); with explicit user sign-off, wrapped invoice+customer+product creation in DB::transaction() to close a real data-corruption gap</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>10 passing tests; re-verified the exact SGST/CGST/IGST amounts from the original GST fix against real live data, digit-for-digit match</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>20. Fixed guest 500 on / (root route)</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>The dashboard route was never behind auth middleware; a logged-out request hit Auth::user()-&gt;name on a null user. Added the auth middleware, matching every other route</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>Guests now get a normal redirect to /login instead of a 500; full test suite is 24/24 passing for the first time</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Commit log continued (this session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>4511c54</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>India-localization pass: timezone, currency, GST fix, language cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>d866e48</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Replace remaining dollar signs and non-Indian flag icon in UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>97f44ec</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Add Oracle Machine Tech seeder; fix Bank model timestamp bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>6f2509c</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Wire dashboard to real business data, remove non-applicable widgets</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>1754e80</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Ignore Laravel compiled view cache and framework cache/session dirs</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>80b7004</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Fix 4 backlog bugs: route shadowing, dead status route, dropped notes, unvalidated placesupply</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>29ab7b9</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Backfill migrations for all live tables + build first real test suite (Phase 0+1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>e995a64</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Quotation domain: tests + Service/Repository refactor (Phase 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>22b1de7</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Home/Auth domain: tests + Service/Repository refactor (Phase 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>9e25bca</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Invoice domain: tests + Service/Repository refactor, largest/last phase (Phase 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>555d9f0</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>Fix guest 500 on / by adding auth middleware to the root route</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Note: of the commits listed above, only the last 6 (80b7004 through 555d9f0 - the backlog bug fixes, migrations/test-infra, and all 4 clean-architecture phases) are unpushed as of this update. 4511c54 through 1754e80 were already pushed to origin/meet-update earlier in this session. Run `git log origin/meet-update..HEAD --oneline` to confirm current status before assuming this is still accurate.</t>
         </is>
       </c>
     </row>
@@ -953,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1428,8 +1862,206 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>🟢 New this session (2026-07-17) — Database schema is now version-controlled</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>18 tables that previously existed ONLY in the live MySQL database — never through a migration — now have real Laravel migrations (database/migrations/2026_07_10_*): invoice, customer, invoiceproduct, paidamount, bank, product, softwaredetails, softerwere1, addlaser, fours, power, motor, gear, rack, cuttingway, cnsthinks, invetry, quationform. These migrations were generated by introspecting the live schema (SHOW CREATE TABLE), so they include the ewaybilldate column from the manual ALTER TABLE step documented further up this sheet — that manual step is now SUPERSEDED for any brand-new environment (the migration creates the column correctly on its own).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>Brand-new environment (empty database)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>Just run: php artisan migrate  —  no manual steps needed anymore, including the old ewaybilldate ALTER TABLE (it's now part of the invoice migration). Then run the seeder if you want sample data: php artisan db:seed --class=OracleMachineTechSeeder</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>MySQL, fresh install</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>All 18 tables get created correctly from scratch, matching the live schema exactly (including its quirks, e.g. bank.update_at instead of updated_at)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>This existing production/dev database (tables already exist, created outside migrations)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Do NOT run php artisan migrate for these 18 blindly — it will try to CREATE TABLE on tables that already exist and fail. They were instead registered as already-applied directly in the migrations table (bookkeeping only, no schema touched). If setting up a NEW copy of THIS specific already-populated database elsewhere, either restore from a mysqldump (schema+data together) or manually insert matching rows into the migrations table with batch numbers after the existing ones - see the actual INSERT statements used this session in the session's commit 29ab7b9 description / conversation log.</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>MySQL, this environment only</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>This DB already had the 18 tables from before migrations existed for them; running the migrations for real here would error with 'table already exists'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>Running the automated test suite</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>php artisan test   (uses .env.testing - sqlite in-memory, migrates fresh automatically for every test class via RefreshDatabase)</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Project root</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>This is what actually unblocks testing - previously there was no way to create a test database at all since 18 core tables had no migrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>🟢 New this session — Application architecture changes affecting deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>What changed</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>Controller namespaces</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>InventryController, QutationController, HomeController, InvoiceController moved from flat App\Http\Controllers\* into App\Http\Controllers\{Inventory,Quotation,Home,Invoice}\* - all matching route references in routes/web.php updated in the same commits</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>None if deploying via git pull (routes/web.php is committed and correct) - only matters if any external tooling/docs hardcoded the old class paths</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>Completes the same Controller -&gt; Service -&gt; Repository pattern already started for Product Configuration in an earlier session</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>.env.testing (new file)</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Committed to git - contains a distinct APP_KEY from production, sqlite :memory: DB, array cache/session drivers</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>None for production; only used when running php artisan test</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>Needed so the test suite doesn't touch the real database</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>New Service/Repository classes</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>app/Services/{Inventory,Quotation,Home,Invoice}/*, app/Repositories/Contracts/*, app/Repositories/Eloquent/* - all new files, bound in app/Providers/RepositoryServiceProvider.php</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>None - behavior preserved exactly, verified by tests + manual smoke testing against live data</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>See Bugs Fixed sheet for the specific bugs found (and left alone) during this refactor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A30:D30"/>
@@ -1960,7 +2592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1981,7 +2613,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 bugs — 2 requested, 4 discovered during verification/QA and fixed proactively</t>
+          <t>11 bugs — 2 originally requested, 9 discovered during verification/QA/refactor passes and fixed</t>
         </is>
       </c>
     </row>
@@ -2194,6 +2826,156 @@
       <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Reproduced and confirmed fixed the same way as #5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>3 routes unreachable (apps-invoices-list, vender, inventrylist)</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>All 3 were single-URL-segment routes registered AFTER the {any} catch-all in routes/web.php, so the catch-all always intercepted them first</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Moved all 3 above the catch-all. apps-invoices-list also had a dead broken query pointing at a nonexistent view (fixed to return the real view); vender's query joined on a nonexistent invoice.customer_id column, discovered only once unshadowed (removed the dead query - view self-queries anyway); inventrylist pointed at a nonexistent controller method (repointed to the existing one)</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>All 3 routes return 200 against real live data, re-verified via curl</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Dead invoice.status route</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>POST route named a controller method that was never implemented; nothing in the app calls it, no stored status column exists to act on</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Removed the route entirely, per explicit product decision (no spec existed for what it should do)</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>Confirmed no other code references this route name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Invoice notes field silently dropped on every save</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>InvoiceController::store() built the create array with key 'note' (singular) but Invoice::$fillable only allows 'notes' (plural) - same mass-assignment bug class as other issues on this sheet</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Fixed the key name</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>Submitted a real invoice with notes text, confirmed it persists in the database</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Invoice creation 500s on empty placesupply</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Column is NOT NULL with no default; no server-side validation existed</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Added $request-&gt;validate(), plus a matching frontend error handler (SweetAlert2) so the failure is visible instead of silent</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>Empty submission now shows a real error (422) instead of a 500; frontend shows a message</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Guest visiting / (dashboard) gets a 500 instead of a login redirect</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>The root route was never wrapped in the auth middleware, so Auth::user()-&gt;name crashed on a null user for any logged-out visitor</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Wrapped the route in auth middleware, matching every other route in the app</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Guest now gets a normal 302 redirect to /login; authenticated access unchanged (re-verified against live data). Full test suite is 24/24 passing as a result</t>
         </is>
       </c>
     </row>
@@ -2777,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2883,27 +3665,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>co2quation route is unreachable</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>CORRECTED 2026-07-17 (was: 'co2quation route is unreachable'): the GET co2quation/{id} form page is NOT shadowed and works fine (re-verified via automated test + live curl, 200) - this entry was stale. The real remaining issue is narrower, see the Co2quationstore row below.</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Shadowed by the app's catch-all {any} route (registered earlier in routes/web.php), and the controller method requires an $id the route never supplies</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Found in an earlier session; fixing requires route re-ordering plus a route-signature decision</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Move the route above the catch-all and add the missing {id} parameter</t>
         </is>
@@ -2960,6 +3742,141 @@
       <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Safe to delete if confirmed unused, or leave as-is</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Co2quationstore route points to a nonexistent controller method</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Medium — the CO2 quotation form's Save button (co2qutation.blade.php) posts to this route and will hard-error if actually submitted</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Route::post('/co2quationstore', ...) names a Co2quationstore() method that has never existed on QutationController, in this session or any prior one</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Confirmed multiple sessions in a row; fixing it means inventing unspecified business logic for what a CO2 quotation save should actually do (no spec, unlike the fiber quotation's generatequtationstore which does exist and work)</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Decide the intended save behavior (likely mirrors generatequtationstore, writing to the same quationform table with different config columns), then implement and add a test</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Quotation list 'Name' column always renders blank</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Low — cosmetic, the list is still usable via email/phone columns</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>listquation.blade.php renders $item-&gt;name; quationform only has a clientname column, no name column exists</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>Found while writing tests/Feature/QuotationTest.php this session; scoped to a refactor pass, not a bug-fixing pass</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Change the view to render $item-&gt;clientname instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Both quotation forms always show product #1's config data</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Medium — any quotation generated from a URL other than product id 1 will show the wrong laser-cutting-machine config options</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>qutation.blade.php, co2qutation.blade.php, and their controller actions all hardcode product_id = 1 and never read the route's {id} parameter</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>Found while writing tests/Feature/QuotationTest.php this session; same bug class as the already-known ProductConfigController hardcoded-product-id issues, so likely needs the same fix applied consistently across both</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Pass the route's {id} through to the config lookup instead of the hardcoded 1, in both places</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Invoice-create page's product dropdown always renders blank option text</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Medium — the dropdown is functionally usable (values/ids are correct) but every option shows blank text, making product selection a guessing game by position</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>apps-invoices-create.blade.php renders $p-&gt;product in the &lt;option&gt; tag; Product only has a name column, never a product column</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Found while writing tests/Feature/InvoiceTest.php this session; scoped to a refactor pass, not a bug-fixing pass</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Change $p-&gt;product to $p-&gt;name in the view</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>layouts/topbar.blade.php still has Velzon demo content</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Low — cosmetic only, doesn't affect functionality</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Search suggestions / notifications / cart panel in the shared topbar still show fake data (e.g. 'Angela Bernier') left over from the original template</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>Flagged multiple sessions ago, never explicitly requested to fix</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Replace with real data or remove the fake panels, if/when requested</t>
         </is>
       </c>
     </row>

--- a/docs/QA-Dev-Work-Log.xlsx
+++ b/docs/QA-Dev-Work-Log.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,6 +209,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -576,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1369,6 +1372,340 @@
       <c r="A53" s="25" t="inlineStr">
         <is>
           <t>Note: of the commits listed above, only the last 6 (80b7004 through 555d9f0 - the backlog bug fixes, migrations/test-infra, and all 4 clean-architecture phases) are unpushed as of this update. 4511c54 through 1754e80 were already pushed to origin/meet-update earlier in this session. Run `git log origin/meet-update..HEAD --oneline` to confirm current status before assuming this is still accurate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Session 3 (2026-07-17): Dynamic Role Matrix (RBAC) - built via subagent-driven development, 8 tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>What was done</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>Detail sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>21. Role matrix: foundation</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>Installed spatie/laravel-permission (no Teams/multi-tenancy - deferred per user decision), added is_active column to users, HasRoles trait on User model, fixed a known RefreshDatabase+Spatie permission-cache staleness gotcha globally in the base TestCase</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>Foundation for all role/permission checks; 27/27 tests passing</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>Manual Commands &amp; Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>22. Role matrix: seeder + factory</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>RolesAndPermissionsSeeder (19 permissions across 9 modules, single source of truth), UserFactory now assigns Owner role by default to every factory-created user</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Owner/Worker seed roles exist; existing tests keep passing without each one needing to know about roles</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>23. Role matrix: login gate</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>Deactivated users (is_active=false) are logged out immediately on login attempt instead of getting full access</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>34/34 tests passing</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>24. Role matrix: Roles &amp; Permissions admin page</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>New Admin\RoleController + matrix UI (checkbox grid, AJAX toggle per permission). Review found and fixed a real gap: role deletion had no safety check and could delete the Owner role itself via a crafted request, silently locking out all admins via a cascading FK - fixed with reassignment/Owner-protection checks at the service layer</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>Dynamic roles work end-to-end; 43/43 tests passing</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>25. Role matrix: Users admin page</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>New Admin\UserController - create/edit-role/activate-deactivate. Owner sets a temporary password directly (no email delivery - not configured in this environment). Proactively added a last-active-Owner lockout guard (same failure class as #24's fix) preventing the sole active Owner from being demoted or deactivated</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>50/50 tests passing</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>26. Role matrix: enforce permissions everywhere</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>Applied permission: middleware to every existing route + gated sidebar links with @can. Found and fixed a genuine pre-existing bug while implementing: /product was silently served by the app's unguarded {any} catch-all route, bypassing auth AND the new permission middleware entirely (confirmed: unauthenticated request returned 500, not a login redirect) - moved into the existing pre-catch-all route group, same pattern already used for 5 other routes</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>Highest-risk task in the plan; independently re-verified by the task reviewer route-by-route against the full permission table, zero mismatches; 54/54 tests passing</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Bugs Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>27. Role matrix: remove signup</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>Auth::routes(['register' =&gt; false]), removed the Signup link, deleted the now-orphaned RegisterController and its view</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>All accounts now admin-created only; 56/56 tests passing</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>28. Role matrix: live rollout</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>Migrated the live MySQL DB (2 new tables/columns), seeded 19 permissions + Owner/Worker roles, assigned Owner role to the 3 real user accounts. Full manual smoke test: Owner reaches all 10 modules incl. new Admin pages; a test Worker with zero permissions correctly 403s everywhere except changing their own password; deactivated Worker correctly blocked from logging back in</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>Live rollout verified end-to-end against real data; test account cleaned up afterward</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>Known Issues (Not Fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Commit log continued (Session 3 - role matrix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="n"/>
+      <c r="D67" s="23" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>cbbb50c</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>Add implementation plan for the dynamic role matrix (RBAC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>5182796</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Add spatie/laravel-permission and is_active column to users</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>51d7938</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>Fix permission count: 19, not 24 (arithmetic error in spec/plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>458505a</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Add RolesAndPermissionsSeeder; UserFactory now assigns Owner role</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>a81e7ed</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>Block login for deactivated users</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>81fac35</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>Add role management + permission matrix UI (incl. deletion-safety fix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>53b4b04</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>Add user management screen (create/edit role/activate-deactivate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>3254c4c</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>Enforce permissions on every existing route + gate sidebar links (incl. /product catch-all fix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>e7cd272</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>Remove public self-registration</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2393,196 @@
       <c r="D46" s="24" t="inlineStr">
         <is>
           <t>See Bugs Fixed sheet for the specific bugs found (and left alone) during this refactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>🔴 MUST RUN on every environment - Role Matrix (RBAC) rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Command / Change</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>php artisan migrate</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>Live MySQL, project root</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t>Creates Spatie's permission tables (roles, permissions, model_has_roles, model_has_permissions, role_has_permissions) and adds users.is_active. Genuinely new tables/columns this time - not the 2026-07-16 backfill situation, no special bookkeeping needed, a normal migrate is correct and sufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>php artisan db:seed --class=RolesAndPermissionsSeeder</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>Live MySQL, project root</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>Creates the 19 fixed permissions and the Owner (all permissions) / Worker (none yet) seed roles. Idempotent - safe to run again if ever needed. Migrations do NOT create roles/permissions themselves, this step is required separately on any environment after migrating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>php artisan tinker --execute="App\Models\User::whereIn('email', [...])-&gt;get()-&gt;each(fn($u) =&gt; $u-&gt;assignRole('Owner'));"</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>Live MySQL, one-time per environment</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>Assigns the Owner role to whichever accounts should have full access on that environment. Run once per environment when rolling this feature out to existing user accounts that predate the role system - see commit 51d7938..e7cd272 range for the full role-matrix feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Role Matrix - what changed for anyone deploying</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>What changed</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>New package dependency</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>spatie/laravel-permission ^6.0 added to composer.json - run composer install on any environment that doesn't already have vendor/spatie</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>Required for the app to boot at all once this feature is deployed (HasRoles trait, permission middleware)</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Standard, actively-maintained package for DB-backed RBAC - not hand-rolled</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>Public registration removed</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>Auth::routes(['register' =&gt; false]) - /register no longer exists, RegisterController.php and register.blade.php deleted</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>Any bookmarked /register link or external reference to it now 404s</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>All accounts are now admin-created via Admin &gt; Users, with an Owner-set temporary password shared directly (no email delivery configured in this environment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>Every existing route now requires a permission</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>See the 19-permission table in docs/superpowers/specs/2026-07-17-role-matrix-design.md - every route in routes/web.php now carries permission: middleware</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>A user with no role/permissions assigned will 403 on everything except their own profile/password pages and the dashboard (if granted dashboard.view)</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Real server-side enforcement, not just hidden UI - by design, per the spec</t>
         </is>
       </c>
     </row>
@@ -2592,7 +3119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2613,7 +3140,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 bugs — 2 originally requested, 9 discovered during verification/QA/refactor passes and fixed</t>
+          <t>13 bugs - 2 originally requested, 11 discovered during verification/QA/refactor passes and fixed</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3503,66 @@
       <c r="F14" s="26" t="inlineStr">
         <is>
           <t>Guest now gets a normal 302 redirect to /login; authenticated access unchanged (re-verified against live data). Full test suite is 24/24 passing as a result</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Role deletion had no safety check (could delete Owner role, locking out all admins)</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>EloquentRoleRepository::delete() was an unconditional Role::find($id)?-&gt;delete(); the permission-tables migration cascades on delete, so an in-use role - including Owner itself - would silently strip it from every assigned user with no recovery path. Only protection was a hideable UI button.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Added checks at the service layer (RoleService::deleteRole): reject deleting the Owner role by name, reject deleting any role with users currently assigned. Controller catches the exception and shows a clean error instead of a 500.</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Found by task review during implementation (not by a user report); fixed and re-reviewed before merge; new tests confirm both the Owner-protection and in-use-role cases are rejected with the role still present in the database afterward</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>/product page was silently served by the app's unguarded catch-all route</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>GET /product matched Route::get('{any}', ...) (registered before the main auth group) before ever reaching the real product route - confirmed via an unauthenticated request returning 500 instead of a login redirect, proving auth middleware never ran either.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Moved the product route into the existing pre-catch-all route group, same pattern already used for 5 other single-segment routes (apps-invoices-list, vender, inventrylist, etc. from an earlier session's fix).</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>Found while adding permission middleware and writing a route-enforcement test; confirmed via curl against the live database that Owner still reaches /product (200) and an unauthenticated visitor now gets a proper redirect, not a 500</t>
         </is>
       </c>
     </row>
@@ -3559,7 +4146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3880,6 +4467,33 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Flashed session messages are never displayed anywhere in the UI</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Low-Medium - the underlying behavior these messages describe (e.g. a deactivated user being blocked from login) works correctly; only the user-facing explanation is missing. A deactivated user sees a plain redirect to the login page with no visible reason why.</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>This is a pre-existing, app-wide pattern: Session::flash('message', ...) / Session::flash('error', ...) is called in several controllers (HomeController's updateProfile/updatePassword, and now LoginController's deactivated-user check), but no Blade layout in this app (including layouts.master-without-nav, which the login page uses) ever renders session('message') or session('error'). Confirmed via a full search - zero views reference either key.</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Found during the role-matrix feature's live smoke test (deactivated test account's login redirect showed no message). Fixing it properly means adding a shared flash-message display block to the relevant layout(s) - a site-wide UI convention, bigger than the role-matrix feature's own scope, and would touch shared layout files used by every page.</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Add a standard Bootstrap alert block reading session('message')/session('error') to layouts/master.blade.php and layouts/master-without-nav.blade.php, styled with the existing alert-class flash value already being set alongside 'message' in the controllers that use it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
